--- a/基本設計/19_ログファイルRedisセキュリティ_基本設計書.xlsx
+++ b/基本設計/19_ログファイルRedisセキュリティ_基本設計書.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rf108ec82ba3c4394"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R466e0b1854604f93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="33_操作ログ" sheetId="34" r:id="R6412fd7a8e4e4739"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="34_ファイル管理" sheetId="35" r:id="R2b0aeadf41114d10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="35_Redis" sheetId="36" r:id="Rd8dd9f9e1efa49d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="36_セキュリティ" sheetId="37" r:id="R55875736cdb04bc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R1b0b09fa2d264664"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R88f1c007e7e44b70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="33_操作ログ" sheetId="34" r:id="R0e0e1b3820d441b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="34_ファイル管理" sheetId="35" r:id="R45e0273376904c88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="35_Redis" sheetId="36" r:id="R974e34587e2647c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="36_セキュリティ" sheetId="37" r:id="R35a822cffbcc4abd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1065,7 +1065,7 @@
     <x:row r="11">
       <x:c r="B11"/>
       <x:c r="C11" s="183" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1088,20 +1088,28 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="D13" s="186" t="str">
-        <x:v>Ver.2.5</x:v>
-      </x:c>
-      <x:c r="E13" s="140"/>
-      <x:c r="F13" s="140"/>
+        <x:v>Ver.2.6</x:v>
+      </x:c>
+      <x:c r="E13" s="140" t="str">
+        <x:v>Ver.2.6</x:v>
+      </x:c>
+      <x:c r="F13" s="140" t="str">
+        <x:v>Ver.2.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="C14" s="177" t="str">
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="D14" s="186" t="str">
-        <x:v>2026-09-24</x:v>
-      </x:c>
-      <x:c r="E14" s="140"/>
-      <x:c r="F14" s="140"/>
+        <x:v>2026-09-28</x:v>
+      </x:c>
+      <x:c r="E14" s="140" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
+      <x:c r="F14" s="140" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="C15" s="177" t="str">
@@ -1118,10 +1126,14 @@
         <x:v>状態</x:v>
       </x:c>
       <x:c r="D16" s="186" t="str">
-        <x:v>Review中</x:v>
-      </x:c>
-      <x:c r="E16" s="140"/>
-      <x:c r="F16" s="140"/>
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="E16" s="140" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="F16" s="140" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="26" customHeight="1">
       <x:c r="A17" s="188"/>
@@ -1145,31 +1157,73 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19"/>
-      <x:c r="C19"/>
-      <x:c r="D19"/>
-      <x:c r="E19"/>
-      <x:c r="F19"/>
-      <x:c r="G19"/>
-      <x:c r="H19"/>
+      <x:c r="B19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="B20"/>
-      <x:c r="C20"/>
-      <x:c r="D20"/>
-      <x:c r="E20"/>
-      <x:c r="F20"/>
-      <x:c r="G20"/>
-      <x:c r="H20"/>
+      <x:c r="B20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="B21" s="182"/>
-      <x:c r="C21" s="182"/>
-      <x:c r="D21" s="182"/>
-      <x:c r="E21" s="182"/>
-      <x:c r="F21" s="182"/>
-      <x:c r="G21" s="182"/>
-      <x:c r="H21" s="182"/>
+      <x:c r="B21" s="182" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="C21" s="182" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="D21" s="182" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="E21" s="182" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="F21" s="182" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="G21" s="182" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
+      <x:c r="H21" s="182" t="str">
+        <x:v>基準Baseline：BL-2026-09-24。変更管理：CHG-AUTH-20260928-01。本改訂はログイン限流・Lock境界の明確化。変更承認後に次Baselineへ組み入れる。</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="B22"/>
@@ -1261,15 +1315,29 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="189" t="str">
-        <x:v>版数：Ver.2.5    改訂日：2026-09-24    Baseline：BL-2026-09-24</x:v>
-      </x:c>
-      <x:c r="B4" s="63"/>
-      <x:c r="C4" s="63"/>
-      <x:c r="D4" s="189"/>
-      <x:c r="E4" s="63"/>
-      <x:c r="F4" s="63"/>
-      <x:c r="G4" s="63"/>
-      <x:c r="H4" s="63"/>
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="B4" s="63" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="C4" s="63" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="D4" s="189" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="E4" s="63" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="F4" s="63" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="G4" s="63" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="H4" s="63" t="str">
+        <x:v>版数：Ver.2.6    改訂日：2026-09-28    基準Baseline：BL-2026-09-24</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
@@ -1607,6 +1675,32 @@
       </x:c>
       <x:c r="H18" s="188" t="str">
         <x:v>BL-2026-09-24。責任者・Review者・承認者はProject Leaderが記入。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="115" customHeight="1">
+      <x:c r="A19" s="184" t="str">
+        <x:v>Ver.2.6</x:v>
+      </x:c>
+      <x:c r="B19" s="184" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
+      <x:c r="C19" s="184" t="str">
+        <x:v>ログイン試行制限の独立固定窓、5回目Lock成立・満了後再開を明確化。CHG-AUTH-20260928-01</x:v>
+      </x:c>
+      <x:c r="D19" s="184" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E19" s="184" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F19" s="184" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G19" s="184" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H19" s="184" t="str">
+        <x:v>変更指示に基づく改訂。新Baseline承認は別途記録。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1672,15 +1766,19 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="189" t="str">
-        <x:v>版数：Ver.2.5</x:v>
-      </x:c>
-      <x:c r="B4" s="63"/>
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
+      <x:c r="B4" s="63" t="str">
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
       <x:c r="C4" s="63"/>
       <x:c r="D4" s="62" t="str"/>
       <x:c r="E4" s="63" t="str">
-        <x:v>2026-09-24</x:v>
-      </x:c>
-      <x:c r="F4" s="63"/>
+        <x:v>2026-09-28</x:v>
+      </x:c>
+      <x:c r="F4" s="63" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
       <x:c r="G4" s="63"/>
       <x:c r="H4" s="63"/>
     </x:row>
@@ -2175,15 +2273,19 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="189" t="str">
-        <x:v>版数：Ver.2.5</x:v>
-      </x:c>
-      <x:c r="B4" s="103"/>
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
+      <x:c r="B4" s="103" t="str">
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
       <x:c r="C4" s="103"/>
       <x:c r="D4" s="118" t="str"/>
       <x:c r="E4" s="63" t="str">
-        <x:v>2026-09-24</x:v>
-      </x:c>
-      <x:c r="F4" s="103"/>
+        <x:v>2026-09-28</x:v>
+      </x:c>
+      <x:c r="F4" s="103" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
       <x:c r="G4" s="103"/>
       <x:c r="H4" s="103"/>
     </x:row>
@@ -2561,15 +2663,19 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="189" t="str">
-        <x:v>版数：Ver.2.5</x:v>
-      </x:c>
-      <x:c r="B4" s="63"/>
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
+      <x:c r="B4" s="63" t="str">
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
       <x:c r="C4" s="63"/>
       <x:c r="D4" s="62" t="str"/>
       <x:c r="E4" s="63" t="str">
-        <x:v>2026-09-24</x:v>
-      </x:c>
-      <x:c r="F4" s="63"/>
+        <x:v>2026-09-28</x:v>
+      </x:c>
+      <x:c r="F4" s="63" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
       <x:c r="G4" s="63"/>
       <x:c r="H4" s="63"/>
     </x:row>
@@ -2647,7 +2753,7 @@
         <x:v>DB=Source,Redis=Cache</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="30" customHeight="1">
+    <x:row r="9" ht="110" customHeight="1">
       <x:c r="A9" s="67" t="str">
         <x:v>Login失敗</x:v>
       </x:c>
@@ -2655,22 +2761,22 @@
         <x:v>auth:login-fail:{username}</x:v>
       </x:c>
       <x:c r="C9" s="67" t="str">
-        <x:v>失敗回数</x:v>
+        <x:v>DB認証失敗回数のCache</x:v>
       </x:c>
       <x:c r="D9" s="67" t="str">
         <x:v>30分</x:v>
       </x:c>
       <x:c r="E9" s="67" t="str">
-        <x:v>失敗時Increment</x:v>
+        <x:v>認証拒否Commit後にDB値を同期。Count値でDB判定を代替しない。</x:v>
       </x:c>
       <x:c r="F9" s="67" t="str">
-        <x:v>成功時Clear/期限</x:v>
+        <x:v>成功時Clear／TTL期限。Lock満了解除は16／28に従い次回Login時DBをReset。</x:v>
       </x:c>
       <x:c r="G9" s="67" t="str">
-        <x:v>users.locked_until</x:v>
+        <x:v>users.failed_login_count／locked_untilを正本として再同期</x:v>
       </x:c>
       <x:c r="H9" s="67" t="str">
-        <x:v>5回で30分Lock</x:v>
+        <x:v>Lock・満了後再開は16／28 BR-AUTH-002。下記Rate Counterとは別用途。TTL消滅だけでDB失敗回数をResetしない。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
@@ -2801,6 +2907,58 @@
       </x:c>
       <x:c r="H14" s="67" t="str">
         <x:v>多重起動防止</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="115" customHeight="1">
+      <x:c r="A15" s="184" t="str">
+        <x:v>Login試行制限（IP）</x:v>
+      </x:c>
+      <x:c r="B15" s="184" t="str">
+        <x:v>login:ip:{ipAddress}</x:v>
+      </x:c>
+      <x:c r="C15" s="184" t="str">
+        <x:v>固定Window内試行数</x:v>
+      </x:c>
+      <x:c r="D15" s="184" t="str">
+        <x:v>初回受付から60秒固定。途中延長なし</x:v>
+      </x:c>
+      <x:c r="E15" s="184" t="str">
+        <x:v>Validation正常Requestを原子的加算。初回TTL設定を同一原子処理で行う。</x:v>
+      </x:c>
+      <x:c r="F15" s="184" t="str">
+        <x:v>TTL満了。Login成功では削除しない。</x:v>
+      </x:c>
+      <x:c r="G15" s="184" t="str">
+        <x:v>障害は認証を開始せずCOMMON-5000</x:v>
+      </x:c>
+      <x:c r="H15" s="184" t="str">
+        <x:v>IP／usernameを独立管理。各10回まで許可。どちらか超過は10／21 AUTH-4290、Retry-After=60。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="115" customHeight="1">
+      <x:c r="A16" s="184" t="str">
+        <x:v>Login試行制限（username）</x:v>
+      </x:c>
+      <x:c r="B16" s="184" t="str">
+        <x:v>login:user:{normalizedUsername}</x:v>
+      </x:c>
+      <x:c r="C16" s="184" t="str">
+        <x:v>固定Window内試行数</x:v>
+      </x:c>
+      <x:c r="D16" s="184" t="str">
+        <x:v>初回受付から60秒固定。途中延長なし</x:v>
+      </x:c>
+      <x:c r="E16" s="184" t="str">
+        <x:v>Trim済username。大小文字保持。IP Keyと同一原子処理で加算。</x:v>
+      </x:c>
+      <x:c r="F16" s="184" t="str">
+        <x:v>TTL満了。Login成功では削除しない。</x:v>
+      </x:c>
+      <x:c r="G16" s="184" t="str">
+        <x:v>障害は認証を開始せずCOMMON-5000</x:v>
+      </x:c>
+      <x:c r="H16" s="184" t="str">
+        <x:v>不一致・成功・制限拒否のいずれも試行数に含める。実装はAPI-AUTH-001／04 Redis-01。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2868,15 +3026,19 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="189" t="str">
-        <x:v>版数：Ver.2.5</x:v>
-      </x:c>
-      <x:c r="B4" s="63"/>
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
+      <x:c r="B4" s="63" t="str">
+        <x:v>版数：Ver.2.6</x:v>
+      </x:c>
       <x:c r="C4" s="63"/>
       <x:c r="D4" s="62" t="str"/>
       <x:c r="E4" s="63" t="str">
-        <x:v>2026-09-24</x:v>
-      </x:c>
-      <x:c r="F4" s="63"/>
+        <x:v>2026-09-28</x:v>
+      </x:c>
+      <x:c r="F4" s="63" t="str">
+        <x:v>2026-09-28</x:v>
+      </x:c>
       <x:c r="G4" s="63"/>
     </x:row>
     <x:row r="5">
@@ -3155,7 +3317,7 @@
       </x:c>
       <x:c r="G18" s="67" t="str"/>
     </x:row>
-    <x:row r="19" ht="30" customHeight="1">
+    <x:row r="19" ht="105" customHeight="1">
       <x:c r="A19" s="67" t="n">
         <x:v>12</x:v>
       </x:c>
@@ -3163,16 +3325,16 @@
         <x:v>Brute Force</x:v>
       </x:c>
       <x:c r="C19" s="67" t="str">
-        <x:v>5回失敗30分Lock + IP/username単位10回/分</x:v>
+        <x:v>Login Lockは16／28 BR-AUTH-002、独立IP／username試行制限は35_Redisを適用。</x:v>
       </x:c>
       <x:c r="D19" s="67" t="str">
-        <x:v>Redis Counter</x:v>
+        <x:v>DB認証状態＋Redis Cache／原子的な固定Window Counter</x:v>
       </x:c>
       <x:c r="E19" s="67" t="str">
         <x:v>M01</x:v>
       </x:c>
       <x:c r="F19" s="67" t="str">
-        <x:v>連続失敗Test</x:v>
+        <x:v>4→5回境界・Lock中照合なし・満了後Reset・独立2制限・10→11回・窓満了・同時受付</x:v>
       </x:c>
       <x:c r="G19" s="67" t="str"/>
     </x:row>
